--- a/outputs/gebaeudemodell/raw/NutzungArt_funktion/gebaeudetypen_auswertung_kumuliert_NutzungArt_funktion.xlsx
+++ b/outputs/gebaeudemodell/raw/NutzungArt_funktion/gebaeudetypen_auswertung_kumuliert_NutzungArt_funktion.xlsx
@@ -499,16 +499,16 @@
         <v>163352235</v>
       </c>
       <c r="F2" t="n">
-        <v>163.352235</v>
+        <v>163.35</v>
       </c>
       <c r="G2" t="n">
-        <v>76.33713742230945</v>
+        <v>76.337</v>
       </c>
       <c r="H2" t="n">
-        <v>163.352235</v>
+        <v>163.35</v>
       </c>
       <c r="I2" t="n">
-        <v>76.33713742230945</v>
+        <v>76.337</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
@@ -531,16 +531,16 @@
         <v>6340192</v>
       </c>
       <c r="F3" t="n">
-        <v>6.340192</v>
+        <v>6.34</v>
       </c>
       <c r="G3" t="n">
-        <v>2.962874110585796</v>
+        <v>2.963</v>
       </c>
       <c r="H3" t="n">
-        <v>169.692427</v>
+        <v>169.69</v>
       </c>
       <c r="I3" t="n">
-        <v>79.30001153289524</v>
+        <v>79.3</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
@@ -563,16 +563,16 @@
         <v>5029282</v>
       </c>
       <c r="F4" t="n">
-        <v>5.029282</v>
+        <v>5.03</v>
       </c>
       <c r="G4" t="n">
-        <v>2.350264697446884</v>
+        <v>2.35</v>
       </c>
       <c r="H4" t="n">
-        <v>174.721709</v>
+        <v>174.72</v>
       </c>
       <c r="I4" t="n">
-        <v>81.65027623034213</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
@@ -595,16 +595,16 @@
         <v>4995591</v>
       </c>
       <c r="F5" t="n">
-        <v>4.995591</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.334520349064415</v>
+        <v>2.335</v>
       </c>
       <c r="H5" t="n">
-        <v>179.7173</v>
+        <v>179.72</v>
       </c>
       <c r="I5" t="n">
-        <v>83.98479657940653</v>
+        <v>83.985</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
@@ -627,16 +627,16 @@
         <v>2894378</v>
       </c>
       <c r="F6" t="n">
-        <v>2.894378</v>
+        <v>2.89</v>
       </c>
       <c r="G6" t="n">
-        <v>1.352589581269636</v>
+        <v>1.353</v>
       </c>
       <c r="H6" t="n">
-        <v>182.611678</v>
+        <v>182.61</v>
       </c>
       <c r="I6" t="n">
-        <v>85.33738616067617</v>
+        <v>85.337</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -659,16 +659,16 @@
         <v>2384166</v>
       </c>
       <c r="F7" t="n">
-        <v>2.384166</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1.114159274157454</v>
+        <v>1.114</v>
       </c>
       <c r="H7" t="n">
-        <v>184.995844</v>
+        <v>185</v>
       </c>
       <c r="I7" t="n">
-        <v>86.45154543483363</v>
+        <v>86.452</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -691,16 +691,16 @@
         <v>2344151</v>
       </c>
       <c r="F8" t="n">
-        <v>2.344151</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>1.095459618447486</v>
+        <v>1.095</v>
       </c>
       <c r="H8" t="n">
-        <v>187.339995</v>
+        <v>187.34</v>
       </c>
       <c r="I8" t="n">
-        <v>87.54700505328113</v>
+        <v>87.547</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
@@ -723,16 +723,16 @@
         <v>2322924</v>
       </c>
       <c r="F9" t="n">
-        <v>2.322924</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>1.085539898548561</v>
+        <v>1.086</v>
       </c>
       <c r="H9" t="n">
-        <v>189.662919</v>
+        <v>189.66</v>
       </c>
       <c r="I9" t="n">
-        <v>88.63254495182969</v>
+        <v>88.633</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -755,16 +755,16 @@
         <v>2164847</v>
       </c>
       <c r="F10" t="n">
-        <v>2.164847</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>1.011667963632541</v>
+        <v>1.012</v>
       </c>
       <c r="H10" t="n">
-        <v>191.827766</v>
+        <v>191.83</v>
       </c>
       <c r="I10" t="n">
-        <v>89.64421291546222</v>
+        <v>89.64400000000001</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
@@ -787,16 +787,16 @@
         <v>2127143</v>
       </c>
       <c r="F11" t="n">
-        <v>2.127143</v>
+        <v>2.13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9940482755433593</v>
+        <v>0.994</v>
       </c>
       <c r="H11" t="n">
-        <v>193.954909</v>
+        <v>193.95</v>
       </c>
       <c r="I11" t="n">
-        <v>90.63826119100558</v>
+        <v>90.63800000000001</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>2024459</v>
       </c>
       <c r="F12" t="n">
-        <v>2.024459</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9460623840796005</v>
+        <v>0.946</v>
       </c>
       <c r="H12" t="n">
-        <v>195.979368</v>
+        <v>195.98</v>
       </c>
       <c r="I12" t="n">
-        <v>91.58432357508518</v>
+        <v>91.584</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
@@ -855,16 +855,16 @@
         <v>1822999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.822999</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8519168726631301</v>
+        <v>0.852</v>
       </c>
       <c r="H13" t="n">
-        <v>197.802367</v>
+        <v>197.8</v>
       </c>
       <c r="I13" t="n">
-        <v>92.43624044774832</v>
+        <v>92.43600000000001</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
@@ -887,16 +887,16 @@
         <v>1518899</v>
       </c>
       <c r="F14" t="n">
-        <v>1.518899</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7098060316934653</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="n">
-        <v>199.321266</v>
+        <v>199.32</v>
       </c>
       <c r="I14" t="n">
-        <v>93.14604647944178</v>
+        <v>93.146</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
@@ -919,16 +919,16 @@
         <v>1013445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.013445</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4735992148191447</v>
+        <v>0.474</v>
       </c>
       <c r="H15" t="n">
-        <v>200.334711</v>
+        <v>200.33</v>
       </c>
       <c r="I15" t="n">
-        <v>93.61964569426092</v>
+        <v>93.62</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
@@ -951,16 +951,16 @@
         <v>864126</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8641259999999999</v>
+        <v>0.86</v>
       </c>
       <c r="G16" t="n">
-        <v>0.403820034737759</v>
+        <v>0.404</v>
       </c>
       <c r="H16" t="n">
-        <v>201.198837</v>
+        <v>201.2</v>
       </c>
       <c r="I16" t="n">
-        <v>94.02346572899867</v>
+        <v>94.023</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
@@ -983,16 +983,16 @@
         <v>863936</v>
       </c>
       <c r="F17" t="n">
-        <v>0.863936</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4037312446694123</v>
+        <v>0.404</v>
       </c>
       <c r="H17" t="n">
-        <v>202.062773</v>
+        <v>202.06</v>
       </c>
       <c r="I17" t="n">
-        <v>94.42719697366809</v>
+        <v>94.42700000000001</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
@@ -1015,16 +1015,16 @@
         <v>717052</v>
       </c>
       <c r="F18" t="n">
-        <v>0.717052</v>
+        <v>0.72</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3350899794113122</v>
+        <v>0.335</v>
       </c>
       <c r="H18" t="n">
-        <v>202.779825</v>
+        <v>202.78</v>
       </c>
       <c r="I18" t="n">
-        <v>94.76228695307941</v>
+        <v>94.762</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
@@ -1047,16 +1047,16 @@
         <v>678714</v>
       </c>
       <c r="F19" t="n">
-        <v>0.678714</v>
+        <v>0.68</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3171740128835417</v>
+        <v>0.317</v>
       </c>
       <c r="H19" t="n">
-        <v>203.458539</v>
+        <v>203.46</v>
       </c>
       <c r="I19" t="n">
-        <v>95.07946096596295</v>
+        <v>95.07899999999999</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1083,16 +1083,16 @@
         <v>656416</v>
       </c>
       <c r="F20" t="n">
-        <v>0.656416</v>
+        <v>0.66</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3067537973888308</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>204.114955</v>
+        <v>204.11</v>
       </c>
       <c r="I20" t="n">
-        <v>95.38621476335179</v>
+        <v>95.386</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
@@ -1115,16 +1115,16 @@
         <v>645068</v>
       </c>
       <c r="F21" t="n">
-        <v>0.645068</v>
+        <v>0.65</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3014506937277859</v>
+        <v>0.301</v>
       </c>
       <c r="H21" t="n">
-        <v>204.760023</v>
+        <v>204.76</v>
       </c>
       <c r="I21" t="n">
-        <v>95.68766545707956</v>
+        <v>95.688</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
@@ -1147,16 +1147,16 @@
         <v>569087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.569087</v>
+        <v>0.57</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2659435453959342</v>
+        <v>0.266</v>
       </c>
       <c r="H22" t="n">
-        <v>205.32911</v>
+        <v>205.33</v>
       </c>
       <c r="I22" t="n">
-        <v>95.9536090024755</v>
+        <v>95.95399999999999</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
@@ -1179,16 +1179,16 @@
         <v>544055</v>
       </c>
       <c r="F23" t="n">
-        <v>0.544055</v>
+        <v>0.54</v>
       </c>
       <c r="G23" t="n">
-        <v>0.254245687549329</v>
+        <v>0.254</v>
       </c>
       <c r="H23" t="n">
-        <v>205.873165</v>
+        <v>205.87</v>
       </c>
       <c r="I23" t="n">
-        <v>96.20785469002483</v>
+        <v>96.208</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
@@ -1211,16 +1211,16 @@
         <v>491136</v>
       </c>
       <c r="F24" t="n">
-        <v>0.491136</v>
+        <v>0.49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2295157842501719</v>
+        <v>0.23</v>
       </c>
       <c r="H24" t="n">
-        <v>206.364301</v>
+        <v>206.36</v>
       </c>
       <c r="I24" t="n">
-        <v>96.437370474275</v>
+        <v>96.437</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
@@ -1243,16 +1243,16 @@
         <v>482869</v>
       </c>
       <c r="F25" t="n">
-        <v>0.482869</v>
+        <v>0.48</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2256524816447913</v>
+        <v>0.226</v>
       </c>
       <c r="H25" t="n">
-        <v>206.84717</v>
+        <v>206.85</v>
       </c>
       <c r="I25" t="n">
-        <v>96.6630229559198</v>
+        <v>96.663</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
@@ -1275,16 +1275,16 @@
         <v>452891</v>
       </c>
       <c r="F26" t="n">
-        <v>0.452891</v>
+        <v>0.45</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2116432781242763</v>
+        <v>0.212</v>
       </c>
       <c r="H26" t="n">
-        <v>207.300061</v>
+        <v>207.3</v>
       </c>
       <c r="I26" t="n">
-        <v>96.87466623404407</v>
+        <v>96.875</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
@@ -1307,16 +1307,16 @@
         <v>446338</v>
       </c>
       <c r="F27" t="n">
-        <v>0.446338</v>
+        <v>0.45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.208580955398613</v>
+        <v>0.209</v>
       </c>
       <c r="H27" t="n">
-        <v>207.746399</v>
+        <v>207.75</v>
       </c>
       <c r="I27" t="n">
-        <v>97.08324718944267</v>
+        <v>97.083</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
@@ -1339,16 +1339,16 @@
         <v>443024</v>
       </c>
       <c r="F28" t="n">
-        <v>0.443024</v>
+        <v>0.44</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2070322696801866</v>
+        <v>0.207</v>
       </c>
       <c r="H28" t="n">
-        <v>208.189423</v>
+        <v>208.19</v>
       </c>
       <c r="I28" t="n">
-        <v>97.29027945912286</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
@@ -1371,16 +1371,16 @@
         <v>436708</v>
       </c>
       <c r="F29" t="n">
-        <v>0.436708</v>
+        <v>0.44</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2040807008818821</v>
+        <v>0.204</v>
       </c>
       <c r="H29" t="n">
-        <v>208.626131</v>
+        <v>208.63</v>
       </c>
       <c r="I29" t="n">
-        <v>97.49436016000475</v>
+        <v>97.494</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
@@ -1403,16 +1403,16 @@
         <v>420059</v>
       </c>
       <c r="F30" t="n">
-        <v>0.420059</v>
+        <v>0.42</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1963003543139638</v>
+        <v>0.196</v>
       </c>
       <c r="H30" t="n">
-        <v>209.04619</v>
+        <v>209.05</v>
       </c>
       <c r="I30" t="n">
-        <v>97.69066051431872</v>
+        <v>97.691</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
@@ -1435,16 +1435,16 @@
         <v>360912</v>
       </c>
       <c r="F31" t="n">
-        <v>0.360912</v>
+        <v>0.36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1686600060376312</v>
+        <v>0.169</v>
       </c>
       <c r="H31" t="n">
-        <v>209.407102</v>
+        <v>209.41</v>
       </c>
       <c r="I31" t="n">
-        <v>97.85932052035633</v>
+        <v>97.85899999999999</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
@@ -1467,16 +1467,16 @@
         <v>341291</v>
       </c>
       <c r="F32" t="n">
-        <v>0.341291</v>
+        <v>0.34</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1594907958743106</v>
+        <v>0.159</v>
       </c>
       <c r="H32" t="n">
-        <v>209.748393</v>
+        <v>209.75</v>
       </c>
       <c r="I32" t="n">
-        <v>98.01881131623065</v>
+        <v>98.01900000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1503,16 +1503,16 @@
         <v>328217</v>
       </c>
       <c r="F33" t="n">
-        <v>0.328217</v>
+        <v>0.33</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1533811045397581</v>
+        <v>0.153</v>
       </c>
       <c r="H33" t="n">
-        <v>210.07661</v>
+        <v>210.08</v>
       </c>
       <c r="I33" t="n">
-        <v>98.17219242077041</v>
+        <v>98.172</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
@@ -1535,16 +1535,16 @@
         <v>321314</v>
       </c>
       <c r="F34" t="n">
-        <v>0.321314</v>
+        <v>0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1501552211618772</v>
+        <v>0.15</v>
       </c>
       <c r="H34" t="n">
-        <v>210.397924</v>
+        <v>210.4</v>
       </c>
       <c r="I34" t="n">
-        <v>98.3223476419323</v>
+        <v>98.322</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
@@ -1567,16 +1567,16 @@
         <v>278464</v>
       </c>
       <c r="F35" t="n">
-        <v>0.278464</v>
+        <v>0.28</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1301307241689468</v>
+        <v>0.13</v>
       </c>
       <c r="H35" t="n">
-        <v>210.676388</v>
+        <v>210.68</v>
       </c>
       <c r="I35" t="n">
-        <v>98.45247836610123</v>
+        <v>98.452</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
@@ -1599,16 +1599,16 @@
         <v>234891</v>
       </c>
       <c r="F36" t="n">
-        <v>0.234891</v>
+        <v>0.23</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1097683576001497</v>
+        <v>0.11</v>
       </c>
       <c r="H36" t="n">
-        <v>210.911279</v>
+        <v>210.91</v>
       </c>
       <c r="I36" t="n">
-        <v>98.56224672370139</v>
+        <v>98.562</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
@@ -1631,16 +1631,16 @@
         <v>225830</v>
       </c>
       <c r="F37" t="n">
-        <v>0.22583</v>
+        <v>0.23</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1055340059723097</v>
+        <v>0.106</v>
       </c>
       <c r="H37" t="n">
-        <v>211.137109</v>
+        <v>211.14</v>
       </c>
       <c r="I37" t="n">
-        <v>98.66778072967369</v>
+        <v>98.66800000000001</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1663,16 +1663,16 @@
         <v>173739</v>
       </c>
       <c r="F38" t="n">
-        <v>0.173739</v>
+        <v>0.17</v>
       </c>
       <c r="G38" t="n">
-        <v>0.08119104044468459</v>
+        <v>0.081</v>
       </c>
       <c r="H38" t="n">
-        <v>211.310848</v>
+        <v>211.31</v>
       </c>
       <c r="I38" t="n">
-        <v>98.74897177011837</v>
+        <v>98.749</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1695,16 +1695,16 @@
         <v>172286</v>
       </c>
       <c r="F39" t="n">
-        <v>0.172286</v>
+        <v>0.17</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0805120300799068</v>
+        <v>0.081</v>
       </c>
       <c r="H39" t="n">
-        <v>211.483134</v>
+        <v>211.48</v>
       </c>
       <c r="I39" t="n">
-        <v>98.82948380019829</v>
+        <v>98.82899999999999</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
@@ -1727,16 +1727,16 @@
         <v>171610</v>
       </c>
       <c r="F40" t="n">
-        <v>0.17161</v>
+        <v>0.17</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08019612436305218</v>
+        <v>0.08</v>
       </c>
       <c r="H40" t="n">
-        <v>211.654744</v>
+        <v>211.65</v>
       </c>
       <c r="I40" t="n">
-        <v>98.90967992456135</v>
+        <v>98.91</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
@@ -1759,16 +1759,16 @@
         <v>156706</v>
       </c>
       <c r="F41" t="n">
-        <v>0.156706</v>
+        <v>0.16</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0732312444754761</v>
+        <v>0.073</v>
       </c>
       <c r="H41" t="n">
-        <v>211.81145</v>
+        <v>211.81</v>
       </c>
       <c r="I41" t="n">
-        <v>98.98291116903681</v>
+        <v>98.983</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -1791,16 +1791,16 @@
         <v>155970</v>
       </c>
       <c r="F42" t="n">
-        <v>0.15597</v>
+        <v>0.16</v>
       </c>
       <c r="G42" t="n">
-        <v>0.07288729978966989</v>
+        <v>0.073</v>
       </c>
       <c r="H42" t="n">
-        <v>211.96742</v>
+        <v>211.97</v>
       </c>
       <c r="I42" t="n">
-        <v>99.05579846882648</v>
+        <v>99.056</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
         <v>154337</v>
       </c>
       <c r="F43" t="n">
-        <v>0.154337</v>
+        <v>0.15</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07212417251803732</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>212.121757</v>
+        <v>212.12</v>
       </c>
       <c r="I43" t="n">
-        <v>99.12792264134453</v>
+        <v>99.128</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -1859,16 +1859,16 @@
         <v>152760</v>
       </c>
       <c r="F44" t="n">
-        <v>0.15276</v>
+        <v>0.15</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07138721495075957</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>212.274517</v>
+        <v>212.27</v>
       </c>
       <c r="I44" t="n">
-        <v>99.19930985629529</v>
+        <v>99.199</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
@@ -1891,16 +1891,16 @@
         <v>136521</v>
       </c>
       <c r="F45" t="n">
-        <v>0.136521</v>
+        <v>0.14</v>
       </c>
       <c r="G45" t="n">
-        <v>0.06379846800401053</v>
+        <v>0.064</v>
       </c>
       <c r="H45" t="n">
-        <v>212.411038</v>
+        <v>212.41</v>
       </c>
       <c r="I45" t="n">
-        <v>99.2631083242993</v>
+        <v>99.26300000000001</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
@@ -1923,16 +1923,16 @@
         <v>119614</v>
       </c>
       <c r="F46" t="n">
-        <v>0.119614</v>
+        <v>0.12</v>
       </c>
       <c r="G46" t="n">
-        <v>0.05589755386960039</v>
+        <v>0.056</v>
       </c>
       <c r="H46" t="n">
-        <v>212.530652</v>
+        <v>212.53</v>
       </c>
       <c r="I46" t="n">
-        <v>99.31900587816889</v>
+        <v>99.319</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
@@ -1955,16 +1955,16 @@
         <v>109977</v>
       </c>
       <c r="F47" t="n">
-        <v>0.109977</v>
+        <v>0.11</v>
       </c>
       <c r="G47" t="n">
-        <v>0.05139402813982513</v>
+        <v>0.051</v>
       </c>
       <c r="H47" t="n">
-        <v>212.640629</v>
+        <v>212.64</v>
       </c>
       <c r="I47" t="n">
-        <v>99.37039990630872</v>
+        <v>99.37</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
@@ -1987,16 +1987,16 @@
         <v>107341</v>
       </c>
       <c r="F48" t="n">
-        <v>0.107341</v>
+        <v>0.11</v>
       </c>
       <c r="G48" t="n">
-        <v>0.05016218277055173</v>
+        <v>0.05</v>
       </c>
       <c r="H48" t="n">
-        <v>212.74797</v>
+        <v>212.75</v>
       </c>
       <c r="I48" t="n">
-        <v>99.42056208907927</v>
+        <v>99.42100000000001</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
@@ -2019,16 +2019,16 @@
         <v>101196</v>
       </c>
       <c r="F49" t="n">
-        <v>0.101196</v>
+        <v>0.1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.04729052503375927</v>
+        <v>0.047</v>
       </c>
       <c r="H49" t="n">
-        <v>212.849166</v>
+        <v>212.85</v>
       </c>
       <c r="I49" t="n">
-        <v>99.46785261411303</v>
+        <v>99.468</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
@@ -2051,16 +2051,16 @@
         <v>83990</v>
       </c>
       <c r="F50" t="n">
-        <v>0.08399</v>
+        <v>0.08</v>
       </c>
       <c r="G50" t="n">
-        <v>0.03924988337074035</v>
+        <v>0.039</v>
       </c>
       <c r="H50" t="n">
-        <v>212.933156</v>
+        <v>212.93</v>
       </c>
       <c r="I50" t="n">
-        <v>99.50710249748377</v>
+        <v>99.50700000000001</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
@@ -2083,16 +2083,16 @@
         <v>79733</v>
       </c>
       <c r="F51" t="n">
-        <v>0.079733</v>
+        <v>0.08</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03726051852362473</v>
+        <v>0.037</v>
       </c>
       <c r="H51" t="n">
-        <v>213.012889</v>
+        <v>213.01</v>
       </c>
       <c r="I51" t="n">
-        <v>99.5443630160074</v>
+        <v>99.544</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -2115,16 +2115,16 @@
         <v>79143</v>
       </c>
       <c r="F52" t="n">
-        <v>0.07914300000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G52" t="n">
-        <v>0.03698480199560072</v>
+        <v>0.037</v>
       </c>
       <c r="H52" t="n">
-        <v>213.092032</v>
+        <v>213.09</v>
       </c>
       <c r="I52" t="n">
-        <v>99.581347818003</v>
+        <v>99.581</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
@@ -2147,16 +2147,16 @@
         <v>77403</v>
       </c>
       <c r="F53" t="n">
-        <v>0.077403</v>
+        <v>0.08</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03617167189600447</v>
+        <v>0.036</v>
       </c>
       <c r="H53" t="n">
-        <v>213.169435</v>
+        <v>213.17</v>
       </c>
       <c r="I53" t="n">
-        <v>99.617519489899</v>
+        <v>99.61799999999999</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
@@ -2179,16 +2179,16 @@
         <v>69976</v>
       </c>
       <c r="F54" t="n">
-        <v>0.069976</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0.03270091485594627</v>
+        <v>0.033</v>
       </c>
       <c r="H54" t="n">
-        <v>213.239411</v>
+        <v>213.24</v>
       </c>
       <c r="I54" t="n">
-        <v>99.65022040475495</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
@@ -2211,16 +2211,16 @@
         <v>68468</v>
       </c>
       <c r="F55" t="n">
-        <v>0.068468</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.03199620210296286</v>
+        <v>0.032</v>
       </c>
       <c r="H55" t="n">
-        <v>213.307879</v>
+        <v>213.31</v>
       </c>
       <c r="I55" t="n">
-        <v>99.68221660685791</v>
+        <v>99.682</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
@@ -2243,16 +2243,16 @@
         <v>68300</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0683</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0319176929898984</v>
+        <v>0.032</v>
       </c>
       <c r="H56" t="n">
-        <v>213.376179</v>
+        <v>213.38</v>
       </c>
       <c r="I56" t="n">
-        <v>99.71413429984781</v>
+        <v>99.714</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
@@ -2275,16 +2275,16 @@
         <v>63240</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06324</v>
+        <v>0.06</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02955307327498059</v>
+        <v>0.03</v>
       </c>
       <c r="H57" t="n">
-        <v>213.439419</v>
+        <v>213.44</v>
       </c>
       <c r="I57" t="n">
-        <v>99.7436873731228</v>
+        <v>99.744</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
@@ -2307,16 +2307,16 @@
         <v>62164</v>
       </c>
       <c r="F58" t="n">
-        <v>0.062164</v>
+        <v>0.06</v>
       </c>
       <c r="G58" t="n">
-        <v>0.02905024109844867</v>
+        <v>0.029</v>
       </c>
       <c r="H58" t="n">
-        <v>213.501583</v>
+        <v>213.5</v>
       </c>
       <c r="I58" t="n">
-        <v>99.77273761422124</v>
+        <v>99.773</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
@@ -2339,16 +2339,16 @@
         <v>56148</v>
       </c>
       <c r="F59" t="n">
-        <v>0.056148</v>
+        <v>0.06</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02623886714490212</v>
+        <v>0.026</v>
       </c>
       <c r="H59" t="n">
-        <v>213.557731</v>
+        <v>213.56</v>
       </c>
       <c r="I59" t="n">
-        <v>99.79897648136614</v>
+        <v>99.79900000000001</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
@@ -2371,16 +2371,16 @@
         <v>50456</v>
       </c>
       <c r="F60" t="n">
-        <v>0.050456</v>
+        <v>0.05</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0235789036236942</v>
+        <v>0.024</v>
       </c>
       <c r="H60" t="n">
-        <v>213.608187</v>
+        <v>213.61</v>
       </c>
       <c r="I60" t="n">
-        <v>99.82255538498983</v>
+        <v>99.82299999999999</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
@@ -2403,16 +2403,16 @@
         <v>46065</v>
       </c>
       <c r="F61" t="n">
-        <v>0.046065</v>
+        <v>0.05</v>
       </c>
       <c r="G61" t="n">
-        <v>0.02152691841258667</v>
+        <v>0.022</v>
       </c>
       <c r="H61" t="n">
-        <v>213.654252</v>
+        <v>213.65</v>
       </c>
       <c r="I61" t="n">
-        <v>99.84408230340243</v>
+        <v>99.84399999999999</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
@@ -2435,16 +2435,16 @@
         <v>38979</v>
       </c>
       <c r="F62" t="n">
-        <v>0.038979</v>
+        <v>0.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01821551617940336</v>
+        <v>0.018</v>
       </c>
       <c r="H62" t="n">
-        <v>213.693231</v>
+        <v>213.69</v>
       </c>
       <c r="I62" t="n">
-        <v>99.86229781958183</v>
+        <v>99.86199999999999</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
@@ -2467,16 +2467,16 @@
         <v>32917</v>
       </c>
       <c r="F63" t="n">
-        <v>0.032917</v>
+        <v>0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01538264568299393</v>
+        <v>0.015</v>
       </c>
       <c r="H63" t="n">
-        <v>213.726148</v>
+        <v>213.73</v>
       </c>
       <c r="I63" t="n">
-        <v>99.87768046526482</v>
+        <v>99.878</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
@@ -2499,16 +2499,16 @@
         <v>32191</v>
       </c>
       <c r="F64" t="n">
-        <v>0.032191</v>
+        <v>0.03</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01504337415867964</v>
+        <v>0.015</v>
       </c>
       <c r="H64" t="n">
-        <v>213.758339</v>
+        <v>213.76</v>
       </c>
       <c r="I64" t="n">
-        <v>99.8927238394235</v>
+        <v>99.893</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
@@ -2531,16 +2531,16 @@
         <v>30930</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03093</v>
+        <v>0.03</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01445408849454696</v>
+        <v>0.014</v>
       </c>
       <c r="H65" t="n">
-        <v>213.789269</v>
+        <v>213.79</v>
       </c>
       <c r="I65" t="n">
-        <v>99.90717792791804</v>
+        <v>99.907</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
@@ -2563,16 +2563,16 @@
         <v>30547</v>
       </c>
       <c r="F66" t="n">
-        <v>0.030547</v>
+        <v>0.03</v>
       </c>
       <c r="G66" t="n">
-        <v>0.01427510640940595</v>
+        <v>0.014</v>
       </c>
       <c r="H66" t="n">
-        <v>213.819816</v>
+        <v>213.82</v>
       </c>
       <c r="I66" t="n">
-        <v>99.92145303432744</v>
+        <v>99.92100000000001</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
@@ -2595,16 +2595,16 @@
         <v>30537</v>
       </c>
       <c r="F67" t="n">
-        <v>0.030537</v>
+        <v>0.03</v>
       </c>
       <c r="G67" t="n">
-        <v>0.01427043324791402</v>
+        <v>0.014</v>
       </c>
       <c r="H67" t="n">
-        <v>213.850353</v>
+        <v>213.85</v>
       </c>
       <c r="I67" t="n">
-        <v>99.93572346757537</v>
+        <v>99.93600000000001</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
@@ -2627,16 +2627,16 @@
         <v>28534</v>
       </c>
       <c r="F68" t="n">
-        <v>0.028534</v>
+        <v>0.03</v>
       </c>
       <c r="G68" t="n">
-        <v>0.01333439900107995</v>
+        <v>0.013</v>
       </c>
       <c r="H68" t="n">
-        <v>213.878887</v>
+        <v>213.88</v>
       </c>
       <c r="I68" t="n">
-        <v>99.94905786657644</v>
+        <v>99.949</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
@@ -2659,16 +2659,16 @@
         <v>21568</v>
       </c>
       <c r="F69" t="n">
-        <v>0.021568</v>
+        <v>0.02</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01007907470579983</v>
+        <v>0.01</v>
       </c>
       <c r="H69" t="n">
-        <v>213.900455</v>
+        <v>213.9</v>
       </c>
       <c r="I69" t="n">
-        <v>99.95913694128224</v>
+        <v>99.959</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
@@ -2691,16 +2691,16 @@
         <v>19562</v>
       </c>
       <c r="F70" t="n">
-        <v>0.019562</v>
+        <v>0.02</v>
       </c>
       <c r="G70" t="n">
-        <v>0.009141638510518191</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>213.920017</v>
+        <v>213.92</v>
       </c>
       <c r="I70" t="n">
-        <v>99.96827857979275</v>
+        <v>99.968</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
@@ -2723,16 +2723,16 @@
         <v>16896</v>
       </c>
       <c r="F71" t="n">
-        <v>0.016896</v>
+        <v>0.02</v>
       </c>
       <c r="G71" t="n">
-        <v>0.007895773656769009</v>
+        <v>0.008</v>
       </c>
       <c r="H71" t="n">
-        <v>213.936913</v>
+        <v>213.94</v>
       </c>
       <c r="I71" t="n">
-        <v>99.97617435344954</v>
+        <v>99.976</v>
       </c>
       <c r="J71" t="inlineStr"/>
     </row>
@@ -2755,16 +2755,16 @@
         <v>11837</v>
       </c>
       <c r="F72" t="n">
-        <v>0.011837</v>
+        <v>0.01</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0055316212580004</v>
+        <v>0.006</v>
       </c>
       <c r="H72" t="n">
-        <v>213.94875</v>
+        <v>213.95</v>
       </c>
       <c r="I72" t="n">
-        <v>99.98170597470754</v>
+        <v>99.982</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
@@ -2787,16 +2787,16 @@
         <v>11235</v>
       </c>
       <c r="F73" t="n">
-        <v>0.011235</v>
+        <v>0.01</v>
       </c>
       <c r="G73" t="n">
-        <v>0.005250296936186069</v>
+        <v>0.005</v>
       </c>
       <c r="H73" t="n">
-        <v>213.959985</v>
+        <v>213.96</v>
       </c>
       <c r="I73" t="n">
-        <v>99.98695627164372</v>
+        <v>99.98699999999999</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
@@ -2819,16 +2819,16 @@
         <v>9409</v>
       </c>
       <c r="F74" t="n">
-        <v>0.009409000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00439697764775921</v>
+        <v>0.004</v>
       </c>
       <c r="H74" t="n">
-        <v>213.969394</v>
+        <v>213.97</v>
       </c>
       <c r="I74" t="n">
-        <v>99.99135324929148</v>
+        <v>99.991</v>
       </c>
       <c r="J74" t="inlineStr"/>
     </row>
@@ -2851,16 +2851,16 @@
         <v>9100</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0091</v>
+        <v>0.01</v>
       </c>
       <c r="G75" t="n">
-        <v>0.004252576957658498</v>
+        <v>0.004</v>
       </c>
       <c r="H75" t="n">
-        <v>213.978494</v>
+        <v>213.98</v>
       </c>
       <c r="I75" t="n">
-        <v>99.99560582624913</v>
+        <v>99.996</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
@@ -2883,16 +2883,16 @@
         <v>4719</v>
       </c>
       <c r="F76" t="n">
-        <v>0.004719</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.002205264908042907</v>
+        <v>0.002</v>
       </c>
       <c r="H76" t="n">
-        <v>213.983213</v>
+        <v>213.98</v>
       </c>
       <c r="I76" t="n">
-        <v>99.99781109115717</v>
+        <v>99.998</v>
       </c>
       <c r="J76" t="inlineStr"/>
     </row>
@@ -2915,16 +2915,16 @@
         <v>4458</v>
       </c>
       <c r="F77" t="n">
-        <v>0.004458</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.002083295393103471</v>
+        <v>0.002</v>
       </c>
       <c r="H77" t="n">
-        <v>213.987671</v>
+        <v>213.99</v>
       </c>
       <c r="I77" t="n">
-        <v>99.99989438655028</v>
+        <v>100</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
@@ -2947,13 +2947,13 @@
         <v>226</v>
       </c>
       <c r="F78" t="n">
-        <v>0.000226</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0001056134497176726</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>213.987897</v>
+        <v>213.99</v>
       </c>
       <c r="I78" t="n">
         <v>100</v>
